--- a/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
@@ -13,15 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'About_This_Data'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Work_Orders'!$A$1:$M$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Technicians'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Control'!$A$1:$B$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Prompt_Log'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Checks'!$A$1:$C$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -561,7 +555,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1331,7 +1324,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="F14" s="2"/>
       <c r="G14" s="4" t="n">
         <v>46278</v>
       </c>
@@ -1971,7 +1964,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="F26" s="2"/>
       <c r="G26" s="4" t="n">
         <v>46266</v>
       </c>
@@ -3259,7 +3252,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr"/>
+      <c r="F50" s="2"/>
       <c r="G50" s="4" t="n">
         <v>46242</v>
       </c>
@@ -4547,7 +4540,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr"/>
+      <c r="F74" s="2"/>
       <c r="G74" s="4" t="n">
         <v>46218</v>
       </c>
@@ -5187,7 +5180,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2"/>
       <c r="G86" s="4" t="n">
         <v>46286</v>
       </c>
@@ -6475,7 +6468,7 @@
           <t>New</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr"/>
+      <c r="F110" s="2"/>
       <c r="G110" s="4" t="n">
         <v>46262</v>
       </c>
@@ -7090,7 +7083,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7296,7 +7288,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -7478,7 +7469,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7625,7 +7615,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7669,12 +7658,82 @@
       </c>
       <c r="B2" s="2">
         <f>ROWS(tblWorkOrders[Work_Order_ID])</f>
-        <v/>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
+      </c>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Claim_or_Test</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source_and_Scope</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>As_At</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Verified_By</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
@@ -545,12 +545,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Rejoin</t>
+          <t>Use</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>This input is a deterministic checkpoint, not proof of your Copilot output.</t>
+          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
         </is>
       </c>
     </row>

--- a/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Work on a copy saved to your OneDrive folder; keep this supplied workbook unchanged.</t>
+          <t>Synthetic training data. Work on this file in your lab folder.</t>
         </is>
       </c>
     </row>
@@ -7530,40 +7530,40 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY</t>
+          <t xml:space="preserve">Money </t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY:
-Inspect tblWorkOrders and Control for Northstar Water Services. State the clean row count, reporting date and recorded cost. Explain why display preferences should not change source values or reporting definitions. Do not edit.</t>
+          <t>Money : show S$ with two decimals
+Dates : show as DD-MMM-YYYY
+Formulas : use structured references
+Answers : start with a one-line summary</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN</t>
+          <t>EXCEL - ALLOW EDITING</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - PLAN:
-Plan a Preference_Check sheet showing Control!B2 reporting date, total work orders and recorded Cost_SGD from tblWorkOrders for Northstar Water Services. Use my saved display and explanation preferences. Preserve Work_Orders, IDs, owners and exact values.
-EXCEL - ALLOW EDITING:
-Apply the reviewed Preference_Check plan with structured-reference formulas. Show a short explanation first and leave the source unchanged.</t>
+          <t>EXCEL - ALLOW EDITING:
+Add a sheet named Preference_Check that shows the reporting date from Control!B2, the number of work orders and the total Cost_SGD, using formulas.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Step 4</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -7574,43 +7574,43 @@
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>EXCEL - ALLOW EDITING:
-In this second Northstar workbook, create Preference_Check with formula-backed Control!B2 reporting date, total work orders and recorded Cost_SGD. Follow my saved preferences, preserve source records and explain the result briefly.</t>
+Just for this task, show the total cost on Preference_Check with four decimal places. Keep the same formula.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - ALLOW EDITING</t>
+          <t>EXCEL - CHAT ONLY</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - ALLOW EDITING:
-For this task only, display the recorded cost result in Preference_Check with four decimal places. Keep its formula and exact numeric value unchanged. Do not modify source cells or my saved preferences.</t>
+          <t>EXCEL - CHAT ONLY:
+In this exercise, which settings belong to my account, which belong to this workbook, and which applied to one prompt only? Answer in three short points.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Step 6</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY</t>
+          <t xml:space="preserve">Excel </t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EXCEL - CHAT ONLY:
-Explain which choices in this exercise belong to my account, which belong to this Northstar workbook and which apply only to one prompt. Use the results I actually observed. Do not claim my preferences are shared with another person or added to the workbook.</t>
+          <t>Excel : Copilot &gt; Settings (...) &gt; Personalization
+Check : your original settings are back</t>
         </is>
       </c>
     </row>

--- a/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-03-personalisation/data/Northstar_Work_Orders.xlsx
@@ -154,9 +154,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:M121" headerRowCount="1">
-  <autoFilter ref="A1:M121"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblWorkOrders" displayName="tblWorkOrders" ref="A1:N121" headerRowCount="1">
+  <autoFilter ref="A1:N121"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="Work_Order_ID"/>
     <tableColumn id="2" name="Site"/>
     <tableColumn id="3" name="Job_Category"/>
@@ -170,6 +170,7 @@
     <tableColumn id="11" name="Actual_Hours"/>
     <tableColumn id="12" name="Cost_SGD"/>
     <tableColumn id="13" name="Description"/>
+    <tableColumn id="14" name="Failure_Mode"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -565,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -581,6 +582,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -649,6 +651,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Failure_Mode</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -704,6 +711,11 @@
           <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -757,6 +769,11 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 002</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -812,6 +829,11 @@
           <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -865,6 +887,11 @@
           <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -918,6 +945,11 @@
           <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -973,6 +1005,11 @@
           <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1026,6 +1063,11 @@
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 007</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -1081,6 +1123,11 @@
           <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1134,6 +1181,11 @@
           <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1187,6 +1239,11 @@
           <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1242,6 +1299,11 @@
           <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1295,6 +1357,11 @@
       <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 012</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1346,6 +1413,11 @@
           <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1399,6 +1471,11 @@
           <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1452,6 +1529,11 @@
           <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1507,6 +1589,11 @@
           <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1560,6 +1647,11 @@
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 017</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1615,6 +1707,11 @@
           <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1668,6 +1765,11 @@
           <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1721,6 +1823,11 @@
           <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1776,6 +1883,11 @@
           <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1829,6 +1941,11 @@
       <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 022</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -1884,6 +2001,11 @@
           <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1937,6 +2059,11 @@
           <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1986,6 +2113,11 @@
           <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2041,6 +2173,11 @@
           <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2094,6 +2231,11 @@
       <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 027</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -2149,6 +2291,11 @@
           <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2202,6 +2349,11 @@
           <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2255,6 +2407,11 @@
           <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2310,6 +2467,11 @@
           <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2363,6 +2525,11 @@
       <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 032</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2418,6 +2585,11 @@
           <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2471,6 +2643,11 @@
           <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2524,6 +2701,11 @@
           <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2579,6 +2761,11 @@
           <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2632,6 +2819,11 @@
       <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 037</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -2687,6 +2879,11 @@
           <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2740,6 +2937,11 @@
           <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2793,6 +2995,11 @@
           <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2848,6 +3055,11 @@
           <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2901,6 +3113,11 @@
       <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 042</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -2956,6 +3173,11 @@
           <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3009,6 +3231,11 @@
           <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3062,6 +3289,11 @@
           <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3117,6 +3349,11 @@
           <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3170,6 +3407,11 @@
       <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 047</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
         </is>
       </c>
     </row>
@@ -3225,6 +3467,11 @@
           <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3274,6 +3521,11 @@
           <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3327,6 +3579,11 @@
           <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3382,6 +3639,11 @@
           <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3435,6 +3697,11 @@
       <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 052</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -3490,6 +3757,11 @@
           <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3543,6 +3815,11 @@
           <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3596,6 +3873,11 @@
           <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3651,6 +3933,11 @@
           <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3704,6 +3991,11 @@
       <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 057</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -3759,6 +4051,11 @@
           <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3812,6 +4109,11 @@
           <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3865,6 +4167,11 @@
           <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3920,6 +4227,11 @@
           <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3973,6 +4285,11 @@
       <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 062</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4028,6 +4345,11 @@
           <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4081,6 +4403,11 @@
           <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4134,6 +4461,11 @@
           <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4189,6 +4521,11 @@
           <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4242,6 +4579,11 @@
       <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 067</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -4297,6 +4639,11 @@
           <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4350,6 +4697,11 @@
           <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4403,6 +4755,11 @@
           <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4458,6 +4815,11 @@
           <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4511,6 +4873,11 @@
       <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 072</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -4562,6 +4929,11 @@
           <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4615,6 +4987,11 @@
           <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4668,6 +5045,11 @@
           <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4723,6 +5105,11 @@
           <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4776,6 +5163,11 @@
       <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 077</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -4831,6 +5223,11 @@
           <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4884,6 +5281,11 @@
           <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4937,6 +5339,11 @@
           <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4992,6 +5399,11 @@
           <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5045,6 +5457,11 @@
       <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 082</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Third-party damage</t>
         </is>
       </c>
     </row>
@@ -5100,6 +5517,11 @@
           <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5153,6 +5575,11 @@
           <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5202,6 +5629,11 @@
           <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5257,6 +5689,11 @@
           <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5310,6 +5747,11 @@
       <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 087</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -5365,6 +5807,11 @@
           <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5418,6 +5865,11 @@
           <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5471,6 +5923,11 @@
           <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5526,6 +5983,11 @@
           <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5579,6 +6041,11 @@
       <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 092</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -5634,6 +6101,11 @@
           <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5687,6 +6159,11 @@
           <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5740,6 +6217,11 @@
           <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5795,6 +6277,11 @@
           <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5848,6 +6335,11 @@
       <c r="M98" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 097</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
@@ -5903,6 +6395,11 @@
           <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Blockage</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5956,6 +6453,11 @@
           <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6009,6 +6511,11 @@
           <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6064,6 +6571,11 @@
           <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6117,6 +6629,11 @@
       <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Leak Repair scheduled or reactive task 102</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6172,6 +6689,11 @@
           <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6225,6 +6747,11 @@
           <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6278,6 +6805,11 @@
           <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6333,6 +6865,11 @@
           <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6386,6 +6923,11 @@
       <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Valve Repair scheduled or reactive task 107</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
         </is>
       </c>
     </row>
@@ -6441,6 +6983,11 @@
           <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Valve seat wear</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6490,6 +7037,11 @@
           <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6543,6 +7095,11 @@
           <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6598,6 +7155,11 @@
           <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6651,6 +7213,11 @@
       <c r="M113" s="2" t="inlineStr">
         <is>
           <t>Pipe Replacement scheduled or reactive task 112</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
         </is>
       </c>
     </row>
@@ -6706,6 +7273,11 @@
           <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Pressure surge</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6759,6 +7331,11 @@
           <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Pump bearing wear</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6812,6 +7389,11 @@
           <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6867,6 +7449,11 @@
           <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6920,6 +7507,11 @@
       <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 117</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Meter fault</t>
         </is>
       </c>
     </row>
@@ -6975,6 +7567,11 @@
           <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Corrosion</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7028,6 +7625,11 @@
           <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7079,6 +7681,11 @@
       <c r="M121" s="2" t="inlineStr">
         <is>
           <t>Meter Service scheduled or reactive task 120</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Joint seal leak</t>
         </is>
       </c>
     </row>
